--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3557-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3557-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B6C6DB4-85CC-4884-881F-26267FA56C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CE26F20-AF2A-486A-AB78-ED9D105D1C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{F4A041A1-87FD-456C-A77E-AFF24B94DCB0}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{3EFB2A0F-7523-44C2-8F33-1DBA7A082AA8}"/>
   </bookViews>
   <sheets>
     <sheet name="3557-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1481,28 +1481,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE24CBB3-DC0B-41B7-9830-362110909072}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E500F2EE-7DBB-46C4-997A-A55431F71E4C}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1536,7 +1536,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1572,7 +1572,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1692,7 +1692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2024</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2023</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2022</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>30</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>30</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="38">
         <v>2021</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>30</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>30</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="36">
         <v>2020</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>30</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>30</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>30</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>30</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2019</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>30</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2018</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2017</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2016</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2015</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2014</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2013</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2012</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2011</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2010</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2009</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2008</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2007</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>8.18</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36" t="s">
         <v>47</v>
       </c>
